--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_biobio.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:24</t>
+    <t xml:space="preserve">2026-09-24 01:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -999,7 +999,7 @@
         <v>-0.75</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>0.25</v>
@@ -1022,7 +1022,7 @@
         <v>-0.22</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>-0.25</v>
@@ -1045,7 +1045,7 @@
         <v>-0.64</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>0.39</v>
@@ -1068,7 +1068,7 @@
         <v>-0.41</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>0.36</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_biobio.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_biobio.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:14</t>
+    <t xml:space="preserve">2026-10-01 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_biobio.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_o_ocup_a_2021_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:10</t>
+    <t xml:space="preserve">2026-10-05 19:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
